--- a/tracking_forms/004_wastewater_testing_appointment_request_form--tracking_forms.xlsx
+++ b/tracking_forms/004_wastewater_testing_appointment_request_form--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[{'id':_1,_'value':_'water_sample',_'label':_'water_sample'}]</t>
+          <t>water_sample</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[{'id': 1, 'value': 'Water sample', 'label': 'Water sample'}]</t>
+          <t>Water sample</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[{'id':_2,_'value':_'wastewater_sample',_'label':_'wastewater_sample'}]</t>
+          <t>wastewater_sample</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[{'id': 2, 'value': 'Wastewater sample', 'label': 'Wastewater sample'}]</t>
+          <t>Wastewater sample</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[{'id':_3,_'value':_'stormwater_sample',_'label':_'stormwater_sample'}]</t>
+          <t>stormwater_sample</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[{'id': 3, 'value': 'Stormwater sample', 'label': 'Stormwater sample'}]</t>
+          <t>Stormwater sample</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[{'id':_4,_'value':_'other',_'label':_'other'}]</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[{'id': 4, 'value': 'Other', 'label': 'Other'}]</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[{'id':_1,_'value':_'lab',_'label':_'lab'}]</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[{'id': 1, 'value': 'Lab', 'label': 'Lab'}]</t>
+          <t>Lab</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[{'id':_2,_'value':_'remote',_'label':_'remote'}]</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[{'id': 2, 'value': 'Remote', 'label': 'Remote'}]</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[{'id':_3,_'value':_'field',_'label':_'field'}]</t>
+          <t>field</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[{'id': 3, 'value': 'Field', 'label': 'Field'}]</t>
+          <t>Field</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[{'id':_4,_'value':_'other',_'label':_'other'}]</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[{'id': 4, 'value': 'Other', 'label': 'Other'}]</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[{'id':_1,_'value':_'once',_'label':_'once'}]</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[{'id': 1, 'value': 'once', 'label': 'once'}]</t>
+          <t>once</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[{'id':_2,_'value':_'daily',_'label':_'daily'}]</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[{'id': 2, 'value': 'daily', 'label': 'daily'}]</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[{'id':_3,_'value':_'weekly',_'label':_'weekly'}]</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[{'id': 3, 'value': 'weekly', 'label': 'weekly'}]</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[{'id':_4,_'value':_'monthly',_'label':_'monthly'}]</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[{'id': 4, 'value': 'monthly', 'label': 'monthly'}]</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[{'id':_1,_'value':_'laboratory_testing',_'label':_'laboratory_testing'}]</t>
+          <t>laboratory_testing</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[{'id': 1, 'value': 'Laboratory Testing', 'label': 'Laboratory Testing'}]</t>
+          <t>Laboratory Testing</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[{'id':_2,_'value':_'onsite_testing',_'label':_'onsite_testing'}]</t>
+          <t>onsite_testing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[{'id': 2, 'value': 'Onsite Testing', 'label': 'Onsite Testing'}]</t>
+          <t>Onsite Testing</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[{'id':_3,_'value':_'field_testing',_'label':_'field_testing'}]</t>
+          <t>field_testing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[{'id': 3, 'value': 'Field Testing', 'label': 'Field Testing'}]</t>
+          <t>Field Testing</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[{'id':_4,_'value':_'other',_'label':_'other'}]</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[{'id': 4, 'value': 'Other', 'label': 'Other'}]</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[{'id':_1,_'value':_'phone',_'label':_'phone'}]</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[{'id': 1, 'value': 'Phone', 'label': 'Phone'}]</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[{'id':_2,_'value':_'email',_'label':_'email'}]</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[{'id': 2, 'value': 'Email', 'label': 'Email'}]</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[{'id':_3,_'value':_'other',_'label':_'other'}]</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[{'id': 3, 'value': 'Other', 'label': 'Other'}]</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[{'id':_1,_'value':_'chatjimmy',_'label':_'chatjimmy'}]</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[{'id': 1, 'value': 'chatjimmy', 'label': 'chatjimmy'}]</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[{'id':_2,_'value':_'other',_'label':_'other'}]</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[{'id': 2, 'value': 'other', 'label': 'other'}]</t>
+          <t>other</t>
         </is>
       </c>
     </row>
